--- a/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
+++ b/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,15 +192,19 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -603,22 +607,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -678,45 +682,45 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="H3" s="9" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="12" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="14" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="R3" s="9" t="n"/>
-      <c r="S3" s="4" t="n"/>
+      <c r="S3" s="16" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -741,7 +745,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -766,7 +770,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -791,7 +795,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -816,515 +820,515 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>09:00〜09:30</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="15" t="n"/>
-      <c r="S5" s="15" t="n"/>
-      <c r="T5" s="15" t="n"/>
-      <c r="U5" s="16" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="20" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="20" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="20" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>09:30〜10:00</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="15" t="n"/>
-      <c r="S6" s="15" t="n"/>
-      <c r="T6" s="15" t="n"/>
-      <c r="U6" s="16" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="n"/>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="20" t="n"/>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="19" t="n"/>
+      <c r="T6" s="19" t="n"/>
+      <c r="U6" s="20" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>10:00〜10:30</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
-      <c r="U7" s="16" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="20" t="n"/>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="19" t="n"/>
+      <c r="T7" s="19" t="n"/>
+      <c r="U7" s="20" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>10:30〜11:00</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
-      <c r="T8" s="15" t="n"/>
-      <c r="U8" s="16" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="20" t="n"/>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="19" t="n"/>
+      <c r="S8" s="19" t="n"/>
+      <c r="T8" s="19" t="n"/>
+      <c r="U8" s="20" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>11:00〜11:30</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="15" t="n"/>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="15" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="15" t="n"/>
-      <c r="T9" s="15" t="n"/>
-      <c r="U9" s="16" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="20" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="19" t="n"/>
+      <c r="T9" s="19" t="n"/>
+      <c r="U9" s="20" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>11:30〜12:00</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="15" t="n"/>
-      <c r="S10" s="15" t="n"/>
-      <c r="T10" s="15" t="n"/>
-      <c r="U10" s="16" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="20" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="n"/>
+      <c r="S10" s="19" t="n"/>
+      <c r="T10" s="19" t="n"/>
+      <c r="U10" s="20" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>12:00〜12:30</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="15" t="n"/>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="15" t="n"/>
-      <c r="T11" s="15" t="n"/>
-      <c r="U11" s="16" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="20" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="19" t="n"/>
+      <c r="T11" s="19" t="n"/>
+      <c r="U11" s="20" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>12:30〜13:00</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="15" t="n"/>
-      <c r="S12" s="15" t="n"/>
-      <c r="T12" s="15" t="n"/>
-      <c r="U12" s="16" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="20" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="19" t="n"/>
+      <c r="T12" s="19" t="n"/>
+      <c r="U12" s="20" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>13:00〜13:30</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="15" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="15" t="n"/>
-      <c r="S13" s="15" t="n"/>
-      <c r="T13" s="15" t="n"/>
-      <c r="U13" s="16" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="20" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="19" t="n"/>
+      <c r="S13" s="19" t="n"/>
+      <c r="T13" s="19" t="n"/>
+      <c r="U13" s="20" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>13:30〜14:00</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="n"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="20" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="19" t="n"/>
+      <c r="T14" s="19" t="n"/>
+      <c r="U14" s="20" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>14:00〜14:30</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="15" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="n"/>
-      <c r="T15" s="15" t="n"/>
-      <c r="U15" s="16" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="20" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="19" t="n"/>
+      <c r="T15" s="19" t="n"/>
+      <c r="U15" s="20" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>14:30〜15:00</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="n"/>
-      <c r="T16" s="15" t="n"/>
-      <c r="U16" s="16" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="19" t="n"/>
+      <c r="S16" s="19" t="n"/>
+      <c r="T16" s="19" t="n"/>
+      <c r="U16" s="20" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>15:00〜15:30</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="n"/>
-      <c r="T17" s="15" t="n"/>
-      <c r="U17" s="16" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="20" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="19" t="n"/>
+      <c r="T17" s="19" t="n"/>
+      <c r="U17" s="20" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>15:30〜16:00</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="n"/>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="16" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="20" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="19" t="n"/>
+      <c r="T18" s="19" t="n"/>
+      <c r="U18" s="20" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>16:00〜16:30</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="n"/>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="16" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="20" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="19" t="n"/>
+      <c r="S19" s="19" t="n"/>
+      <c r="T19" s="19" t="n"/>
+      <c r="U19" s="20" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>16:30〜17:00</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
-      <c r="T20" s="15" t="n"/>
-      <c r="U20" s="16" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="19" t="n"/>
+      <c r="S20" s="19" t="n"/>
+      <c r="T20" s="19" t="n"/>
+      <c r="U20" s="20" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>17:00〜17:30</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="16" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="19" t="n"/>
+      <c r="S21" s="19" t="n"/>
+      <c r="T21" s="19" t="n"/>
+      <c r="U21" s="20" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>17:30〜18:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
-      <c r="T22" s="15" t="n"/>
-      <c r="U22" s="16" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="20" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="19" t="n"/>
+      <c r="S22" s="19" t="n"/>
+      <c r="T22" s="19" t="n"/>
+      <c r="U22" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>【使い方】対応可=✅で受付OK（担当不在・休憩・ブロックは✅を外す）／来店=当日ご来店で✅／担当者・集客経路はドロップダウン選択</t>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>【使い方】新規対応=✅で新規受付OK（不在・休憩・ブロックは✅を外す）／対応者=枠ごとにドロップダウンで選択／来店=当日ご来店で✅／集客経路はドロップダウン選択</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="R3:U3"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A24:U24"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q2:U2"/>
     <mergeCell ref="G2:K2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:U1"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B22">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B5="✅"</formula>
+      <formula>NOT(ISBLANK(B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F22">
@@ -1334,7 +1338,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G22">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>G5="✅"</formula>
+      <formula>NOT(ISBLANK(G5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K22">
@@ -1344,7 +1348,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>L5="✅"</formula>
+      <formula>NOT(ISBLANK(L5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P22">
@@ -1354,7 +1358,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q22">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>Q5="✅"</formula>
+      <formula>NOT(ISBLANK(Q5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U22">
@@ -1363,13 +1367,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C3 H3 M3 R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$A$2:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$C$2:$C$8</formula1>
     </dataValidation>
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 H3 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 M3 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 R3 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1388,22 +1392,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -1463,45 +1467,45 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="H3" s="9" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="12" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="14" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="R3" s="9" t="n"/>
-      <c r="S3" s="4" t="n"/>
+      <c r="S3" s="16" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1526,7 +1530,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1551,7 +1555,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1576,7 +1580,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -1601,515 +1605,515 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>09:00〜09:30</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="15" t="n"/>
-      <c r="S5" s="15" t="n"/>
-      <c r="T5" s="15" t="n"/>
-      <c r="U5" s="16" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="20" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="20" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="20" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>09:30〜10:00</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="15" t="n"/>
-      <c r="S6" s="15" t="n"/>
-      <c r="T6" s="15" t="n"/>
-      <c r="U6" s="16" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="n"/>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="20" t="n"/>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="19" t="n"/>
+      <c r="T6" s="19" t="n"/>
+      <c r="U6" s="20" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>10:00〜10:30</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
-      <c r="U7" s="16" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="20" t="n"/>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="19" t="n"/>
+      <c r="T7" s="19" t="n"/>
+      <c r="U7" s="20" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>10:30〜11:00</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
-      <c r="T8" s="15" t="n"/>
-      <c r="U8" s="16" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="20" t="n"/>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="19" t="n"/>
+      <c r="S8" s="19" t="n"/>
+      <c r="T8" s="19" t="n"/>
+      <c r="U8" s="20" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>11:00〜11:30</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="15" t="n"/>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="15" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="15" t="n"/>
-      <c r="T9" s="15" t="n"/>
-      <c r="U9" s="16" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="20" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="19" t="n"/>
+      <c r="T9" s="19" t="n"/>
+      <c r="U9" s="20" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>11:30〜12:00</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="15" t="n"/>
-      <c r="S10" s="15" t="n"/>
-      <c r="T10" s="15" t="n"/>
-      <c r="U10" s="16" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="20" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="n"/>
+      <c r="S10" s="19" t="n"/>
+      <c r="T10" s="19" t="n"/>
+      <c r="U10" s="20" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>12:00〜12:30</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="15" t="n"/>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="15" t="n"/>
-      <c r="T11" s="15" t="n"/>
-      <c r="U11" s="16" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="20" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="19" t="n"/>
+      <c r="T11" s="19" t="n"/>
+      <c r="U11" s="20" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>12:30〜13:00</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="15" t="n"/>
-      <c r="S12" s="15" t="n"/>
-      <c r="T12" s="15" t="n"/>
-      <c r="U12" s="16" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="20" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="19" t="n"/>
+      <c r="T12" s="19" t="n"/>
+      <c r="U12" s="20" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>13:00〜13:30</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="15" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="15" t="n"/>
-      <c r="S13" s="15" t="n"/>
-      <c r="T13" s="15" t="n"/>
-      <c r="U13" s="16" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="20" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="19" t="n"/>
+      <c r="S13" s="19" t="n"/>
+      <c r="T13" s="19" t="n"/>
+      <c r="U13" s="20" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>13:30〜14:00</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="n"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="20" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="19" t="n"/>
+      <c r="T14" s="19" t="n"/>
+      <c r="U14" s="20" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>14:00〜14:30</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="15" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="n"/>
-      <c r="T15" s="15" t="n"/>
-      <c r="U15" s="16" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="20" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="19" t="n"/>
+      <c r="T15" s="19" t="n"/>
+      <c r="U15" s="20" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>14:30〜15:00</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="n"/>
-      <c r="T16" s="15" t="n"/>
-      <c r="U16" s="16" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="19" t="n"/>
+      <c r="S16" s="19" t="n"/>
+      <c r="T16" s="19" t="n"/>
+      <c r="U16" s="20" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>15:00〜15:30</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="n"/>
-      <c r="T17" s="15" t="n"/>
-      <c r="U17" s="16" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="20" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="19" t="n"/>
+      <c r="T17" s="19" t="n"/>
+      <c r="U17" s="20" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>15:30〜16:00</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="n"/>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="16" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="20" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="19" t="n"/>
+      <c r="T18" s="19" t="n"/>
+      <c r="U18" s="20" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>16:00〜16:30</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="n"/>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="16" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="20" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="19" t="n"/>
+      <c r="S19" s="19" t="n"/>
+      <c r="T19" s="19" t="n"/>
+      <c r="U19" s="20" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>16:30〜17:00</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
-      <c r="T20" s="15" t="n"/>
-      <c r="U20" s="16" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="19" t="n"/>
+      <c r="S20" s="19" t="n"/>
+      <c r="T20" s="19" t="n"/>
+      <c r="U20" s="20" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>17:00〜17:30</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="16" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="19" t="n"/>
+      <c r="S21" s="19" t="n"/>
+      <c r="T21" s="19" t="n"/>
+      <c r="U21" s="20" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>17:30〜18:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
-      <c r="T22" s="15" t="n"/>
-      <c r="U22" s="16" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="20" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="19" t="n"/>
+      <c r="S22" s="19" t="n"/>
+      <c r="T22" s="19" t="n"/>
+      <c r="U22" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>【使い方】対応可=✅で受付OK（担当不在・休憩・ブロックは✅を外す）／来店=当日ご来店で✅／担当者・集客経路はドロップダウン選択</t>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>【使い方】新規対応=✅で新規受付OK（不在・休憩・ブロックは✅を外す）／対応者=枠ごとにドロップダウンで選択／来店=当日ご来店で✅／集客経路はドロップダウン選択</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="R3:U3"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A24:U24"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q2:U2"/>
     <mergeCell ref="G2:K2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:U1"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B22">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B5="✅"</formula>
+      <formula>NOT(ISBLANK(B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F22">
@@ -2119,7 +2123,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G22">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>G5="✅"</formula>
+      <formula>NOT(ISBLANK(G5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K22">
@@ -2129,7 +2133,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>L5="✅"</formula>
+      <formula>NOT(ISBLANK(L5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P22">
@@ -2139,7 +2143,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q22">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>Q5="✅"</formula>
+      <formula>NOT(ISBLANK(Q5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U22">
@@ -2148,13 +2152,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C3 H3 M3 R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$A$2:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$C$2:$C$8</formula1>
     </dataValidation>
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 H3 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 M3 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 R3 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2173,22 +2177,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="6" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
@@ -2248,45 +2252,45 @@
     <row r="3">
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>担当者</t>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="C3" s="9" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="10" t="n"/>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="10" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="H3" s="9" t="n"/>
-      <c r="I3" s="4" t="n"/>
+      <c r="I3" s="12" t="n"/>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="M3" s="9" t="n"/>
-      <c r="N3" s="4" t="n"/>
+      <c r="N3" s="14" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="12" t="inlineStr">
-        <is>
-          <t>担当者</t>
+      <c r="Q3" s="15" t="inlineStr">
+        <is>
+          <t>新規対応</t>
         </is>
       </c>
       <c r="R3" s="9" t="n"/>
-      <c r="S3" s="4" t="n"/>
+      <c r="S3" s="16" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2336,7 +2340,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>対応可</t>
+          <t>対応者</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
@@ -2386,515 +2390,515 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>09:00〜09:30</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="15" t="n"/>
-      <c r="D5" s="15" t="n"/>
-      <c r="E5" s="15" t="n"/>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="15" t="n"/>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="15" t="n"/>
-      <c r="K5" s="16" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="15" t="n"/>
-      <c r="N5" s="15" t="n"/>
-      <c r="O5" s="15" t="n"/>
-      <c r="P5" s="16" t="n"/>
-      <c r="Q5" s="14" t="n"/>
-      <c r="R5" s="15" t="n"/>
-      <c r="S5" s="15" t="n"/>
-      <c r="T5" s="15" t="n"/>
-      <c r="U5" s="16" t="n"/>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="n"/>
+      <c r="D5" s="19" t="n"/>
+      <c r="E5" s="19" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="18" t="n"/>
+      <c r="H5" s="19" t="n"/>
+      <c r="I5" s="19" t="n"/>
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="20" t="n"/>
+      <c r="L5" s="18" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="20" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="20" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>09:30〜10:00</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="16" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="15" t="n"/>
-      <c r="J6" s="15" t="n"/>
-      <c r="K6" s="16" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="15" t="n"/>
-      <c r="P6" s="16" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="15" t="n"/>
-      <c r="S6" s="15" t="n"/>
-      <c r="T6" s="15" t="n"/>
-      <c r="U6" s="16" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="19" t="n"/>
+      <c r="D6" s="19" t="n"/>
+      <c r="E6" s="19" t="n"/>
+      <c r="F6" s="20" t="n"/>
+      <c r="G6" s="18" t="n"/>
+      <c r="H6" s="19" t="n"/>
+      <c r="I6" s="19" t="n"/>
+      <c r="J6" s="19" t="n"/>
+      <c r="K6" s="20" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="M6" s="19" t="n"/>
+      <c r="N6" s="19" t="n"/>
+      <c r="O6" s="19" t="n"/>
+      <c r="P6" s="20" t="n"/>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="19" t="n"/>
+      <c r="S6" s="19" t="n"/>
+      <c r="T6" s="19" t="n"/>
+      <c r="U6" s="20" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>10:00〜10:30</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="15" t="n"/>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="15" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="15" t="n"/>
-      <c r="J7" s="15" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="14" t="n"/>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n"/>
-      <c r="P7" s="16" t="n"/>
-      <c r="Q7" s="14" t="n"/>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n"/>
-      <c r="T7" s="15" t="n"/>
-      <c r="U7" s="16" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="19" t="n"/>
+      <c r="D7" s="19" t="n"/>
+      <c r="E7" s="19" t="n"/>
+      <c r="F7" s="20" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="20" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="19" t="n"/>
+      <c r="P7" s="20" t="n"/>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="19" t="n"/>
+      <c r="S7" s="19" t="n"/>
+      <c r="T7" s="19" t="n"/>
+      <c r="U7" s="20" t="n"/>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>10:30〜11:00</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="15" t="n"/>
-      <c r="D8" s="15" t="n"/>
-      <c r="E8" s="15" t="n"/>
-      <c r="F8" s="16" t="n"/>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="15" t="n"/>
-      <c r="I8" s="15" t="n"/>
-      <c r="J8" s="15" t="n"/>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="15" t="n"/>
-      <c r="N8" s="15" t="n"/>
-      <c r="O8" s="15" t="n"/>
-      <c r="P8" s="16" t="n"/>
-      <c r="Q8" s="14" t="n"/>
-      <c r="R8" s="15" t="n"/>
-      <c r="S8" s="15" t="n"/>
-      <c r="T8" s="15" t="n"/>
-      <c r="U8" s="16" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="19" t="n"/>
+      <c r="D8" s="19" t="n"/>
+      <c r="E8" s="19" t="n"/>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n"/>
+      <c r="I8" s="19" t="n"/>
+      <c r="J8" s="19" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="19" t="n"/>
+      <c r="N8" s="19" t="n"/>
+      <c r="O8" s="19" t="n"/>
+      <c r="P8" s="20" t="n"/>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="19" t="n"/>
+      <c r="S8" s="19" t="n"/>
+      <c r="T8" s="19" t="n"/>
+      <c r="U8" s="20" t="n"/>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>11:00〜11:30</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="15" t="n"/>
-      <c r="D9" s="15" t="n"/>
-      <c r="E9" s="15" t="n"/>
-      <c r="F9" s="16" t="n"/>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="15" t="n"/>
-      <c r="J9" s="15" t="n"/>
-      <c r="K9" s="16" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="15" t="n"/>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="15" t="n"/>
-      <c r="P9" s="16" t="n"/>
-      <c r="Q9" s="14" t="n"/>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="15" t="n"/>
-      <c r="T9" s="15" t="n"/>
-      <c r="U9" s="16" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="n"/>
+      <c r="D9" s="19" t="n"/>
+      <c r="E9" s="19" t="n"/>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="19" t="n"/>
+      <c r="I9" s="19" t="n"/>
+      <c r="J9" s="19" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="19" t="n"/>
+      <c r="N9" s="19" t="n"/>
+      <c r="O9" s="19" t="n"/>
+      <c r="P9" s="20" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="19" t="n"/>
+      <c r="S9" s="19" t="n"/>
+      <c r="T9" s="19" t="n"/>
+      <c r="U9" s="20" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>11:30〜12:00</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="15" t="n"/>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="16" t="n"/>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="15" t="n"/>
-      <c r="J10" s="15" t="n"/>
-      <c r="K10" s="16" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="15" t="n"/>
-      <c r="P10" s="16" t="n"/>
-      <c r="Q10" s="14" t="n"/>
-      <c r="R10" s="15" t="n"/>
-      <c r="S10" s="15" t="n"/>
-      <c r="T10" s="15" t="n"/>
-      <c r="U10" s="16" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="19" t="n"/>
+      <c r="D10" s="19" t="n"/>
+      <c r="E10" s="19" t="n"/>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="19" t="n"/>
+      <c r="I10" s="19" t="n"/>
+      <c r="J10" s="19" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="M10" s="19" t="n"/>
+      <c r="N10" s="19" t="n"/>
+      <c r="O10" s="19" t="n"/>
+      <c r="P10" s="20" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="19" t="n"/>
+      <c r="S10" s="19" t="n"/>
+      <c r="T10" s="19" t="n"/>
+      <c r="U10" s="20" t="n"/>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>12:00〜12:30</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="16" t="n"/>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="15" t="n"/>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n"/>
-      <c r="P11" s="16" t="n"/>
-      <c r="Q11" s="14" t="n"/>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="15" t="n"/>
-      <c r="T11" s="15" t="n"/>
-      <c r="U11" s="16" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="19" t="n"/>
+      <c r="D11" s="19" t="n"/>
+      <c r="E11" s="19" t="n"/>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="19" t="n"/>
+      <c r="I11" s="19" t="n"/>
+      <c r="J11" s="19" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="19" t="n"/>
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n"/>
+      <c r="P11" s="20" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="19" t="n"/>
+      <c r="T11" s="19" t="n"/>
+      <c r="U11" s="20" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>12:30〜13:00</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="15" t="n"/>
-      <c r="D12" s="15" t="n"/>
-      <c r="E12" s="15" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="15" t="n"/>
-      <c r="I12" s="15" t="n"/>
-      <c r="J12" s="15" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="15" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="15" t="n"/>
-      <c r="S12" s="15" t="n"/>
-      <c r="T12" s="15" t="n"/>
-      <c r="U12" s="16" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="19" t="n"/>
+      <c r="D12" s="19" t="n"/>
+      <c r="E12" s="19" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n"/>
+      <c r="I12" s="19" t="n"/>
+      <c r="J12" s="19" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="19" t="n"/>
+      <c r="N12" s="19" t="n"/>
+      <c r="O12" s="19" t="n"/>
+      <c r="P12" s="20" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="19" t="n"/>
+      <c r="S12" s="19" t="n"/>
+      <c r="T12" s="19" t="n"/>
+      <c r="U12" s="20" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>13:00〜13:30</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="15" t="n"/>
-      <c r="J13" s="15" t="n"/>
-      <c r="K13" s="16" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="15" t="n"/>
-      <c r="P13" s="16" t="n"/>
-      <c r="Q13" s="14" t="n"/>
-      <c r="R13" s="15" t="n"/>
-      <c r="S13" s="15" t="n"/>
-      <c r="T13" s="15" t="n"/>
-      <c r="U13" s="16" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="19" t="n"/>
+      <c r="D13" s="19" t="n"/>
+      <c r="E13" s="19" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="19" t="n"/>
+      <c r="I13" s="19" t="n"/>
+      <c r="J13" s="19" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="M13" s="19" t="n"/>
+      <c r="N13" s="19" t="n"/>
+      <c r="O13" s="19" t="n"/>
+      <c r="P13" s="20" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="19" t="n"/>
+      <c r="S13" s="19" t="n"/>
+      <c r="T13" s="19" t="n"/>
+      <c r="U13" s="20" t="n"/>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>13:30〜14:00</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="16" t="n"/>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="15" t="n"/>
-      <c r="J14" s="15" t="n"/>
-      <c r="K14" s="16" t="n"/>
-      <c r="L14" s="14" t="n"/>
-      <c r="M14" s="15" t="n"/>
-      <c r="N14" s="15" t="n"/>
-      <c r="O14" s="15" t="n"/>
-      <c r="P14" s="16" t="n"/>
-      <c r="Q14" s="14" t="n"/>
-      <c r="R14" s="15" t="n"/>
-      <c r="S14" s="15" t="n"/>
-      <c r="T14" s="15" t="n"/>
-      <c r="U14" s="16" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="20" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="19" t="n"/>
+      <c r="P14" s="20" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="19" t="n"/>
+      <c r="S14" s="19" t="n"/>
+      <c r="T14" s="19" t="n"/>
+      <c r="U14" s="20" t="n"/>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>14:00〜14:30</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="14" t="n"/>
-      <c r="H15" s="15" t="n"/>
-      <c r="I15" s="15" t="n"/>
-      <c r="J15" s="15" t="n"/>
-      <c r="K15" s="16" t="n"/>
-      <c r="L15" s="14" t="n"/>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="15" t="n"/>
-      <c r="P15" s="16" t="n"/>
-      <c r="Q15" s="14" t="n"/>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="n"/>
-      <c r="T15" s="15" t="n"/>
-      <c r="U15" s="16" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="20" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n"/>
+      <c r="P15" s="20" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="19" t="n"/>
+      <c r="T15" s="19" t="n"/>
+      <c r="U15" s="20" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>14:30〜15:00</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="15" t="n"/>
-      <c r="D16" s="15" t="n"/>
-      <c r="E16" s="15" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="15" t="n"/>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="16" t="n"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="15" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-      <c r="R16" s="15" t="n"/>
-      <c r="S16" s="15" t="n"/>
-      <c r="T16" s="15" t="n"/>
-      <c r="U16" s="16" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+      <c r="K16" s="20" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="19" t="n"/>
+      <c r="N16" s="19" t="n"/>
+      <c r="O16" s="19" t="n"/>
+      <c r="P16" s="20" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="19" t="n"/>
+      <c r="S16" s="19" t="n"/>
+      <c r="T16" s="19" t="n"/>
+      <c r="U16" s="20" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>15:00〜15:30</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="15" t="n"/>
-      <c r="I17" s="15" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="16" t="n"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="15" t="n"/>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="n"/>
-      <c r="T17" s="15" t="n"/>
-      <c r="U17" s="16" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
+      <c r="K17" s="20" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="19" t="n"/>
+      <c r="N17" s="19" t="n"/>
+      <c r="O17" s="19" t="n"/>
+      <c r="P17" s="20" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="19" t="n"/>
+      <c r="S17" s="19" t="n"/>
+      <c r="T17" s="19" t="n"/>
+      <c r="U17" s="20" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>15:30〜16:00</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="15" t="n"/>
-      <c r="J18" s="15" t="n"/>
-      <c r="K18" s="16" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="15" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="15" t="n"/>
-      <c r="S18" s="15" t="n"/>
-      <c r="T18" s="15" t="n"/>
-      <c r="U18" s="16" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="19" t="n"/>
+      <c r="D18" s="19" t="n"/>
+      <c r="E18" s="19" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="19" t="n"/>
+      <c r="I18" s="19" t="n"/>
+      <c r="J18" s="19" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="19" t="n"/>
+      <c r="N18" s="19" t="n"/>
+      <c r="O18" s="19" t="n"/>
+      <c r="P18" s="20" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="19" t="n"/>
+      <c r="S18" s="19" t="n"/>
+      <c r="T18" s="19" t="n"/>
+      <c r="U18" s="20" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>16:00〜16:30</t>
         </is>
       </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="15" t="n"/>
-      <c r="J19" s="15" t="n"/>
-      <c r="K19" s="16" t="n"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="15" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-      <c r="R19" s="15" t="n"/>
-      <c r="S19" s="15" t="n"/>
-      <c r="T19" s="15" t="n"/>
-      <c r="U19" s="16" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="19" t="n"/>
+      <c r="D19" s="19" t="n"/>
+      <c r="E19" s="19" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="19" t="n"/>
+      <c r="I19" s="19" t="n"/>
+      <c r="J19" s="19" t="n"/>
+      <c r="K19" s="20" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="19" t="n"/>
+      <c r="N19" s="19" t="n"/>
+      <c r="O19" s="19" t="n"/>
+      <c r="P19" s="20" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="19" t="n"/>
+      <c r="S19" s="19" t="n"/>
+      <c r="T19" s="19" t="n"/>
+      <c r="U19" s="20" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>16:30〜17:00</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="16" t="n"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="15" t="n"/>
-      <c r="N20" s="15" t="n"/>
-      <c r="O20" s="15" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-      <c r="R20" s="15" t="n"/>
-      <c r="S20" s="15" t="n"/>
-      <c r="T20" s="15" t="n"/>
-      <c r="U20" s="16" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="19" t="n"/>
+      <c r="D20" s="19" t="n"/>
+      <c r="E20" s="19" t="n"/>
+      <c r="F20" s="20" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="19" t="n"/>
+      <c r="I20" s="19" t="n"/>
+      <c r="J20" s="19" t="n"/>
+      <c r="K20" s="20" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="19" t="n"/>
+      <c r="N20" s="19" t="n"/>
+      <c r="O20" s="19" t="n"/>
+      <c r="P20" s="20" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="19" t="n"/>
+      <c r="S20" s="19" t="n"/>
+      <c r="T20" s="19" t="n"/>
+      <c r="U20" s="20" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>17:00〜17:30</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="14" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="15" t="n"/>
-      <c r="J21" s="15" t="n"/>
-      <c r="K21" s="16" t="n"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="15" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-      <c r="R21" s="15" t="n"/>
-      <c r="S21" s="15" t="n"/>
-      <c r="T21" s="15" t="n"/>
-      <c r="U21" s="16" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="19" t="n"/>
+      <c r="D21" s="19" t="n"/>
+      <c r="E21" s="19" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="19" t="n"/>
+      <c r="I21" s="19" t="n"/>
+      <c r="J21" s="19" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="19" t="n"/>
+      <c r="N21" s="19" t="n"/>
+      <c r="O21" s="19" t="n"/>
+      <c r="P21" s="20" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="19" t="n"/>
+      <c r="S21" s="19" t="n"/>
+      <c r="T21" s="19" t="n"/>
+      <c r="U21" s="20" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>17:30〜18:00</t>
         </is>
       </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="15" t="n"/>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="14" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="15" t="n"/>
-      <c r="J22" s="15" t="n"/>
-      <c r="K22" s="16" t="n"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="15" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-      <c r="R22" s="15" t="n"/>
-      <c r="S22" s="15" t="n"/>
-      <c r="T22" s="15" t="n"/>
-      <c r="U22" s="16" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="19" t="n"/>
+      <c r="D22" s="19" t="n"/>
+      <c r="E22" s="19" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="19" t="n"/>
+      <c r="I22" s="19" t="n"/>
+      <c r="J22" s="19" t="n"/>
+      <c r="K22" s="20" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="19" t="n"/>
+      <c r="N22" s="19" t="n"/>
+      <c r="O22" s="19" t="n"/>
+      <c r="P22" s="20" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="19" t="n"/>
+      <c r="S22" s="19" t="n"/>
+      <c r="T22" s="19" t="n"/>
+      <c r="U22" s="20" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>【使い方】対応可=✅で受付OK（担当不在・休憩・ブロックは✅を外す）／来店=当日ご来店で✅／担当者・集客経路はドロップダウン選択</t>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>【使い方】新規対応=✅で新規受付OK（不在・休憩・ブロックは✅を外す）／対応者=枠ごとにドロップダウンで選択／来店=当日ご来店で✅／集客経路はドロップダウン選択</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="R3:U3"/>
     <mergeCell ref="L2:P2"/>
-    <mergeCell ref="C3:F3"/>
     <mergeCell ref="A24:U24"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A2:A4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q2:U2"/>
     <mergeCell ref="G2:K2"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="S3:U3"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:U1"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:B22">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>B5="✅"</formula>
+      <formula>NOT(ISBLANK(B5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5:F22">
@@ -2904,7 +2908,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G22">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>G5="✅"</formula>
+      <formula>NOT(ISBLANK(G5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K5:K22">
@@ -2914,7 +2918,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="L5:L22">
     <cfRule type="expression" priority="5" dxfId="0">
-      <formula>L5="✅"</formula>
+      <formula>NOT(ISBLANK(L5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P5:P22">
@@ -2924,7 +2928,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="Q5:Q22">
     <cfRule type="expression" priority="7" dxfId="0">
-      <formula>Q5="✅"</formula>
+      <formula>NOT(ISBLANK(Q5))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U5:U22">
@@ -2933,13 +2937,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="C3 H3 M3 R3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$A$2:$A$7</formula1>
     </dataValidation>
     <dataValidation sqref="E5 E6 E7 E8 E9 E10 E11 E12 E13 E14 E15 E16 E17 E18 E19 E20 E21 E22 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 O5 O6 O7 O8 O9 O10 O11 O12 O13 O14 O15 O16 O17 O18 O19 O20 O21 O22 T5 T6 T7 T8 T9 T10 T11 T12 T13 T14 T15 T16 T17 T18 T19 T20 T21 T22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=設定!$C$2:$C$8</formula1>
     </dataValidation>
-    <dataValidation sqref="B5 B6 B7 B8 B9 B10 B11 B12 B13 B14 B15 B16 B17 B18 B19 B20 B21 B22 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 Q5 Q6 Q7 Q8 Q9 Q10 Q11 Q12 Q13 Q14 Q15 Q16 Q17 Q18 Q19 Q20 Q21 Q22 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C3 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14 F15 F16 F17 F18 F19 F20 F21 F22 H3 K5 K6 K7 K8 K9 K10 K11 K12 K13 K14 K15 K16 K17 K18 K19 K20 K21 K22 M3 P5 P6 P7 P8 P9 P10 P11 P12 P13 P14 P15 P16 P17 P18 P19 P20 P21 P22 R3 U5 U6 U7 U8 U9 U10 U11 U12 U13 U14 U15 U16 U17 U18 U19 U20 U21 U22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✅"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2963,17 +2967,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>担当者リスト</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>集客経路リスト</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="22" t="inlineStr">
         <is>
           <t>チェック</t>
         </is>

--- a/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
+++ b/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
@@ -165,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -221,6 +221,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2958,12 +2967,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2977,9 +2988,24 @@
           <t>集客経路リスト</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
-        <is>
-          <t>チェック</t>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>集計</t>
+        </is>
+      </c>
+      <c r="E1" s="23" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+      <c r="F1" s="23" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+      <c r="G1" s="23" t="inlineStr">
+        <is>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2990,10 +3016,17 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
+      <c r="E2" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C2)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C2)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C2)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C2)</f>
+        <v/>
+      </c>
+      <c r="F2" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C2)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C2)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C2)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C2)</f>
+        <v/>
+      </c>
+      <c r="G2" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C2)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C2)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C2)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C2)</f>
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -3007,6 +3040,18 @@
           <t>Googleマップ</t>
         </is>
       </c>
+      <c r="E3" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C3)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C3)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C3)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C3)</f>
+        <v/>
+      </c>
+      <c r="F3" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C3)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C3)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C3)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C3)</f>
+        <v/>
+      </c>
+      <c r="G3" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C3)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C3)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C3)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3019,6 +3064,18 @@
           <t>チラシ</t>
         </is>
       </c>
+      <c r="E4" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C4)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C4)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C4)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C4)</f>
+        <v/>
+      </c>
+      <c r="F4" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C4)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C4)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C4)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C4)</f>
+        <v/>
+      </c>
+      <c r="G4" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C4)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C4)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C4)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3031,6 +3088,18 @@
           <t>紹介</t>
         </is>
       </c>
+      <c r="E5" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C5)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C5)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C5)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C5)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C5)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C5)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C5)</f>
+        <v/>
+      </c>
+      <c r="G5" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C5)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C5)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C5)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3043,6 +3112,18 @@
           <t>HP</t>
         </is>
       </c>
+      <c r="E6" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C6)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C6)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C6)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C6)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C6)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C6)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C6)</f>
+        <v/>
+      </c>
+      <c r="G6" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C6)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C6)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C6)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3055,12 +3136,55 @@
           <t>既存会員</t>
         </is>
       </c>
+      <c r="E7" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C7)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C7)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C7)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C7)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C7)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C7)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C7)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C7)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C7)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
+      </c>
+      <c r="E8" s="24">
+        <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C8)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C8)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C8)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C8)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C8)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C8)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="24">
+        <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C8)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C8)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C8)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="E9" s="25">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>SUM(G2:G8)</f>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
+++ b/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
@@ -10,7 +10,8 @@
     <sheet name="8月28日（金）" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="8月29日（土）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="8月30日（日）" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="設定" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="体験者一覧" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="設定" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -165,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -219,6 +220,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2963,6 +2967,67 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>体験日</t>
+        </is>
+      </c>
+      <c r="B1" s="22" t="inlineStr">
+        <is>
+          <t>氏名</t>
+        </is>
+      </c>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="D1" s="22" t="inlineStr">
+        <is>
+          <t>集客きっかけ</t>
+        </is>
+      </c>
+      <c r="E1" s="22" t="inlineStr">
+        <is>
+          <t>次回予約（〇・×）</t>
+        </is>
+      </c>
+      <c r="F1" s="22" t="inlineStr">
+        <is>
+          <t>次回来店日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>IFERROR(LET(data,VSTACK(HSTACK(IF('8月28日（金）'!$C$5:$C$22&lt;&gt;"","8/28",""),'8月28日（金）'!$C$5:$C$22,'8月28日（金）'!$B$5:$B$22,'8月28日（金）'!$E$5:$E$22),HSTACK(IF('8月28日（金）'!$H$5:$H$22&lt;&gt;"","8/28",""),'8月28日（金）'!$H$5:$H$22,'8月28日（金）'!$G$5:$G$22,'8月28日（金）'!$J$5:$J$22),HSTACK(IF('8月28日（金）'!$M$5:$M$22&lt;&gt;"","8/28",""),'8月28日（金）'!$M$5:$M$22,'8月28日（金）'!$L$5:$L$22,'8月28日（金）'!$O$5:$O$22),HSTACK(IF('8月28日（金）'!$R$5:$R$22&lt;&gt;"","8/28",""),'8月28日（金）'!$R$5:$R$22,'8月28日（金）'!$Q$5:$Q$22,'8月28日（金）'!$T$5:$T$22),HSTACK(IF('8月29日（土）'!$C$5:$C$22&lt;&gt;"","8/29",""),'8月29日（土）'!$C$5:$C$22,'8月29日（土）'!$B$5:$B$22,'8月29日（土）'!$E$5:$E$22),HSTACK(IF('8月29日（土）'!$H$5:$H$22&lt;&gt;"","8/29",""),'8月29日（土）'!$H$5:$H$22,'8月29日（土）'!$G$5:$G$22,'8月29日（土）'!$J$5:$J$22),HSTACK(IF('8月29日（土）'!$M$5:$M$22&lt;&gt;"","8/29",""),'8月29日（土）'!$M$5:$M$22,'8月29日（土）'!$L$5:$L$22,'8月29日（土）'!$O$5:$O$22),HSTACK(IF('8月29日（土）'!$R$5:$R$22&lt;&gt;"","8/29",""),'8月29日（土）'!$R$5:$R$22,'8月29日（土）'!$Q$5:$Q$22,'8月29日（土）'!$T$5:$T$22),HSTACK(IF('8月30日（日）'!$C$5:$C$22&lt;&gt;"","8/30",""),'8月30日（日）'!$C$5:$C$22,'8月30日（日）'!$B$5:$B$22,'8月30日（日）'!$E$5:$E$22),HSTACK(IF('8月30日（日）'!$H$5:$H$22&lt;&gt;"","8/30",""),'8月30日（日）'!$H$5:$H$22,'8月30日（日）'!$G$5:$G$22,'8月30日（日）'!$J$5:$J$22),HSTACK(IF('8月30日（日）'!$M$5:$M$22&lt;&gt;"","8/30",""),'8月30日（日）'!$M$5:$M$22,'8月30日（日）'!$L$5:$L$22,'8月30日（日）'!$O$5:$O$22),HSTACK(IF('8月30日（日）'!$R$5:$R$22&lt;&gt;"","8/30",""),'8月30日（日）'!$R$5:$R$22,'8月30日（日）'!$Q$5:$Q$22,'8月30日（日）'!$T$5:$T$22)),FILTER(data,INDEX(data,,2)&lt;&gt;"")),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2978,32 +3043,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>担当者リスト</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>集客経路リスト</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>集計</t>
         </is>
       </c>
-      <c r="E1" s="23" t="inlineStr">
+      <c r="E1" s="24" t="inlineStr">
         <is>
           <t>8/28</t>
         </is>
       </c>
-      <c r="F1" s="23" t="inlineStr">
+      <c r="F1" s="24" t="inlineStr">
         <is>
           <t>8/29</t>
         </is>
       </c>
-      <c r="G1" s="23" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>8/30</t>
         </is>
@@ -3016,15 +3081,15 @@
           <t>Instagram</t>
         </is>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C2)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C2)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C2)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C2)</f>
         <v/>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C2)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C2)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C2)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C2)</f>
         <v/>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C2)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C2)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C2)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C2)</f>
         <v/>
       </c>
@@ -3040,15 +3105,15 @@
           <t>Googleマップ</t>
         </is>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C3)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C3)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C3)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C3)</f>
         <v/>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C3)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C3)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C3)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C3)</f>
         <v/>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C3)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C3)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C3)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C3)</f>
         <v/>
       </c>
@@ -3064,15 +3129,15 @@
           <t>チラシ</t>
         </is>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C4)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C4)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C4)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C4)</f>
         <v/>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C4)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C4)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C4)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C4)</f>
         <v/>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C4)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C4)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C4)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C4)</f>
         <v/>
       </c>
@@ -3088,15 +3153,15 @@
           <t>紹介</t>
         </is>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C5)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C5)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C5)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C5)</f>
         <v/>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C5)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C5)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C5)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C5)</f>
         <v/>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C5)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C5)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C5)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C5)</f>
         <v/>
       </c>
@@ -3112,15 +3177,15 @@
           <t>HP</t>
         </is>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C6)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C6)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C6)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C6)</f>
         <v/>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C6)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C6)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C6)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C6)</f>
         <v/>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C6)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C6)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C6)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C6)</f>
         <v/>
       </c>
@@ -3136,15 +3201,15 @@
           <t>既存会員</t>
         </is>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C7)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C7)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C7)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C7)</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C7)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C7)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C7)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C7)</f>
         <v/>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C7)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C7)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C7)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C7)</f>
         <v/>
       </c>
@@ -3155,34 +3220,34 @@
           <t>その他</t>
         </is>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>COUNTIF('8月28日（金）'!$E$5:$E$22,$C8)+COUNTIF('8月28日（金）'!$J$5:$J$22,$C8)+COUNTIF('8月28日（金）'!$O$5:$O$22,$C8)+COUNTIF('8月28日（金）'!$T$5:$T$22,$C8)</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>COUNTIF('8月29日（土）'!$E$5:$E$22,$C8)+COUNTIF('8月29日（土）'!$J$5:$J$22,$C8)+COUNTIF('8月29日（土）'!$O$5:$O$22,$C8)+COUNTIF('8月29日（土）'!$T$5:$T$22,$C8)</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <f>COUNTIF('8月30日（日）'!$E$5:$E$22,$C8)+COUNTIF('8月30日（日）'!$J$5:$J$22,$C8)+COUNTIF('8月30日（日）'!$O$5:$O$22,$C8)+COUNTIF('8月30日（日）'!$T$5:$T$22,$C8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>SUM(F2:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>SUM(G2:G8)</f>
         <v/>
       </c>

--- a/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
+++ b/ONE'S BODY静岡安倍川店_体験会予約表.xlsx
@@ -3016,7 +3016,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <f>IFERROR(LET(data,VSTACK(HSTACK(IF('8月28日（金）'!$C$5:$C$22&lt;&gt;"","8/28",""),'8月28日（金）'!$C$5:$C$22,'8月28日（金）'!$B$5:$B$22,'8月28日（金）'!$E$5:$E$22),HSTACK(IF('8月28日（金）'!$H$5:$H$22&lt;&gt;"","8/28",""),'8月28日（金）'!$H$5:$H$22,'8月28日（金）'!$G$5:$G$22,'8月28日（金）'!$J$5:$J$22),HSTACK(IF('8月28日（金）'!$M$5:$M$22&lt;&gt;"","8/28",""),'8月28日（金）'!$M$5:$M$22,'8月28日（金）'!$L$5:$L$22,'8月28日（金）'!$O$5:$O$22),HSTACK(IF('8月28日（金）'!$R$5:$R$22&lt;&gt;"","8/28",""),'8月28日（金）'!$R$5:$R$22,'8月28日（金）'!$Q$5:$Q$22,'8月28日（金）'!$T$5:$T$22),HSTACK(IF('8月29日（土）'!$C$5:$C$22&lt;&gt;"","8/29",""),'8月29日（土）'!$C$5:$C$22,'8月29日（土）'!$B$5:$B$22,'8月29日（土）'!$E$5:$E$22),HSTACK(IF('8月29日（土）'!$H$5:$H$22&lt;&gt;"","8/29",""),'8月29日（土）'!$H$5:$H$22,'8月29日（土）'!$G$5:$G$22,'8月29日（土）'!$J$5:$J$22),HSTACK(IF('8月29日（土）'!$M$5:$M$22&lt;&gt;"","8/29",""),'8月29日（土）'!$M$5:$M$22,'8月29日（土）'!$L$5:$L$22,'8月29日（土）'!$O$5:$O$22),HSTACK(IF('8月29日（土）'!$R$5:$R$22&lt;&gt;"","8/29",""),'8月29日（土）'!$R$5:$R$22,'8月29日（土）'!$Q$5:$Q$22,'8月29日（土）'!$T$5:$T$22),HSTACK(IF('8月30日（日）'!$C$5:$C$22&lt;&gt;"","8/30",""),'8月30日（日）'!$C$5:$C$22,'8月30日（日）'!$B$5:$B$22,'8月30日（日）'!$E$5:$E$22),HSTACK(IF('8月30日（日）'!$H$5:$H$22&lt;&gt;"","8/30",""),'8月30日（日）'!$H$5:$H$22,'8月30日（日）'!$G$5:$G$22,'8月30日（日）'!$J$5:$J$22),HSTACK(IF('8月30日（日）'!$M$5:$M$22&lt;&gt;"","8/30",""),'8月30日（日）'!$M$5:$M$22,'8月30日（日）'!$L$5:$L$22,'8月30日（日）'!$O$5:$O$22),HSTACK(IF('8月30日（日）'!$R$5:$R$22&lt;&gt;"","8/30",""),'8月30日（日）'!$R$5:$R$22,'8月30日（日）'!$Q$5:$Q$22,'8月30日（日）'!$T$5:$T$22)),FILTER(data,INDEX(data,,2)&lt;&gt;"")),"")</f>
+        <f>IFERROR(LET(data,VSTACK(HSTACK(ARRAYFORMULA(IF('8月28日（金）'!$C$5:$C$22&lt;&gt;"","8/28","")),'8月28日（金）'!$C$5:$C$22,'8月28日（金）'!$B$5:$B$22,'8月28日（金）'!$E$5:$E$22),HSTACK(ARRAYFORMULA(IF('8月28日（金）'!$H$5:$H$22&lt;&gt;"","8/28","")),'8月28日（金）'!$H$5:$H$22,'8月28日（金）'!$G$5:$G$22,'8月28日（金）'!$J$5:$J$22),HSTACK(ARRAYFORMULA(IF('8月28日（金）'!$M$5:$M$22&lt;&gt;"","8/28","")),'8月28日（金）'!$M$5:$M$22,'8月28日（金）'!$L$5:$L$22,'8月28日（金）'!$O$5:$O$22),HSTACK(ARRAYFORMULA(IF('8月28日（金）'!$R$5:$R$22&lt;&gt;"","8/28","")),'8月28日（金）'!$R$5:$R$22,'8月28日（金）'!$Q$5:$Q$22,'8月28日（金）'!$T$5:$T$22),HSTACK(ARRAYFORMULA(IF('8月29日（土）'!$C$5:$C$22&lt;&gt;"","8/29","")),'8月29日（土）'!$C$5:$C$22,'8月29日（土）'!$B$5:$B$22,'8月29日（土）'!$E$5:$E$22),HSTACK(ARRAYFORMULA(IF('8月29日（土）'!$H$5:$H$22&lt;&gt;"","8/29","")),'8月29日（土）'!$H$5:$H$22,'8月29日（土）'!$G$5:$G$22,'8月29日（土）'!$J$5:$J$22),HSTACK(ARRAYFORMULA(IF('8月29日（土）'!$M$5:$M$22&lt;&gt;"","8/29","")),'8月29日（土）'!$M$5:$M$22,'8月29日（土）'!$L$5:$L$22,'8月29日（土）'!$O$5:$O$22),HSTACK(ARRAYFORMULA(IF('8月29日（土）'!$R$5:$R$22&lt;&gt;"","8/29","")),'8月29日（土）'!$R$5:$R$22,'8月29日（土）'!$Q$5:$Q$22,'8月29日（土）'!$T$5:$T$22),HSTACK(ARRAYFORMULA(IF('8月30日（日）'!$C$5:$C$22&lt;&gt;"","8/30","")),'8月30日（日）'!$C$5:$C$22,'8月30日（日）'!$B$5:$B$22,'8月30日（日）'!$E$5:$E$22),HSTACK(ARRAYFORMULA(IF('8月30日（日）'!$H$5:$H$22&lt;&gt;"","8/30","")),'8月30日（日）'!$H$5:$H$22,'8月30日（日）'!$G$5:$G$22,'8月30日（日）'!$J$5:$J$22),HSTACK(ARRAYFORMULA(IF('8月30日（日）'!$M$5:$M$22&lt;&gt;"","8/30","")),'8月30日（日）'!$M$5:$M$22,'8月30日（日）'!$L$5:$L$22,'8月30日（日）'!$O$5:$O$22),HSTACK(ARRAYFORMULA(IF('8月30日（日）'!$R$5:$R$22&lt;&gt;"","8/30","")),'8月30日（日）'!$R$5:$R$22,'8月30日（日）'!$Q$5:$Q$22,'8月30日（日）'!$T$5:$T$22)),FILTER(data,INDEX(data,,2)&lt;&gt;"")),"")</f>
         <v/>
       </c>
     </row>
